--- a/Thesis_TSSP_NEWNEW_M1_Results_3_Scenarios.xlsx
+++ b/Thesis_TSSP_NEWNEW_M1_Results_3_Scenarios.xlsx
@@ -483,12 +483,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Infeed Station 2</t>
+          <t>Infeed Station 3</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>4/5/2026 10:49</t>
+          <t>4/5/2026 09:55</t>
         </is>
       </c>
     </row>
@@ -500,12 +500,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Unload Gate 3</t>
+          <t>Unload Gate 4</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>4/5/2026 15:14</t>
+          <t>4/5/2026 11:34</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -537,7 +537,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Unload Gate 2</t>
+          <t>Unload Gate 4</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -574,12 +574,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Unload Gate 4</t>
+          <t>Unload Gate 2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>4/5/2026 15:14</t>
+          <t>4/5/2026 09:53</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Infeed Station 2</t>
+          <t>Infeed Station 3</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>4/5/2026 11:52</t>
+          <t>4/5/2026 11:50</t>
         </is>
       </c>
     </row>
@@ -611,12 +611,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Unload Gate 3</t>
+          <t>Unload Gate 4</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>4/5/2026 10:39</t>
+          <t>4/5/2026 15:14</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -648,24 +648,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Unload Gate 1</t>
+          <t>Unload Gate 2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>4/5/2026 09:20</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Transport Cart 3</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>4/5/2026 15:14</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Transport Cart 1</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>4/5/2026 07:57</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>Infeed Station 2</t>
@@ -673,7 +673,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>4/5/2026 07:30</t>
+          <t>4/5/2026 07:32</t>
         </is>
       </c>
     </row>
@@ -705,12 +705,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Infeed Station 1</t>
+          <t>Infeed Station 2</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>4/5/2026 06:58</t>
+          <t>4/5/2026 07:00</t>
         </is>
       </c>
     </row>
@@ -759,27 +759,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Unload Gate 1</t>
+          <t>Unload Gate 3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>4/5/2026 08:29</t>
+          <t>4/5/2026 08:49</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Transport Cart 1</t>
+          <t>Transport Cart 3</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>4/5/2026 11:25</t>
+          <t>4/5/2026 12:12</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Infeed Station 2</t>
+          <t>Infeed Station 3</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -796,12 +796,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Unload Gate 1</t>
+          <t>Unload Gate 4</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>4/5/2026 15:10</t>
+          <t>4/5/2026 11:14</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Infeed Station 2</t>
+          <t>Infeed Station 1</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>4/5/2026 08:36</t>
+          <t>4/5/2026 09:34</t>
         </is>
       </c>
     </row>
@@ -870,22 +870,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Unload Gate 4</t>
+          <t>Unload Gate 3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>4/5/2026 12:31</t>
+          <t>4/5/2026 12:28</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Transport Cart 1</t>
+          <t>Transport Cart 3</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>4/5/2026 15:09</t>
+          <t>4/5/2026 13:47</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>4/5/2026 11:14</t>
+          <t>4/5/2026 11:26</t>
         </is>
       </c>
     </row>
@@ -907,32 +907,32 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Unload Gate 1</t>
+          <t>Unload Gate 4</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>4/5/2026 12:21</t>
+          <t>4/5/2026 12:38</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Transport Cart 1</t>
+          <t>Transport Cart 2</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>4/5/2026 08:43</t>
+          <t>4/5/2026 09:21</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Infeed Station 3</t>
+          <t>Infeed Station 2</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>4/5/2026 11:07</t>
+          <t>4/5/2026 10:48</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Transport Cart 3</t>
+          <t>Transport Cart 1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>4/5/2026 06:21</t>
+          <t>4/5/2026 06:20</t>
         </is>
       </c>
     </row>
@@ -981,12 +981,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Unload Gate 4</t>
+          <t>Unload Gate 3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>4/5/2026 13:03</t>
+          <t>4/5/2026 13:10</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1001,12 +1001,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Infeed Station 3</t>
+          <t>Infeed Station 1</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>4/5/2026 07:26</t>
+          <t>4/5/2026 07:22</t>
         </is>
       </c>
     </row>
@@ -1018,12 +1018,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Unload Gate 3</t>
+          <t>Unload Gate 4</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>4/5/2026 14:34</t>
+          <t>4/5/2026 13:36</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1038,12 +1038,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Infeed Station 3</t>
+          <t>Infeed Station 2</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>4/5/2026 09:19</t>
+          <t>4/5/2026 09:17</t>
         </is>
       </c>
     </row>
@@ -1055,12 +1055,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Unload Gate 1</t>
+          <t>Unload Gate 2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>4/5/2026 15:11</t>
+          <t>4/5/2026 13:01</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1092,22 +1092,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Unload Gate 1</t>
+          <t>Unload Gate 2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>4/5/2026 14:11</t>
+          <t>4/5/2026 13:42</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Transport Cart 3</t>
+          <t>Transport Cart 2</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>4/5/2026 10:47</t>
+          <t>4/5/2026 12:02</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>4/5/2026 09:37</t>
+          <t>4/5/2026 09:36</t>
         </is>
       </c>
     </row>
@@ -1129,12 +1129,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Unload Gate 4</t>
+          <t>Unload Gate 2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>4/5/2026 09:01</t>
+          <t>4/5/2026 08:20</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1149,12 +1149,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Infeed Station 2</t>
+          <t>Infeed Station 3</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>4/5/2026 10:06</t>
+          <t>4/5/2026 10:31</t>
         </is>
       </c>
     </row>
@@ -1166,12 +1166,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Unload Gate 3</t>
+          <t>Unload Gate 1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>4/5/2026 12:06</t>
+          <t>4/5/2026 12:38</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1186,12 +1186,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Infeed Station 3</t>
+          <t>Infeed Station 2</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>4/5/2026 10:16</t>
+          <t>4/5/2026 10:34</t>
         </is>
       </c>
     </row>
@@ -1203,22 +1203,22 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Unload Gate 4</t>
+          <t>Unload Gate 3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>4/5/2026 14:28</t>
+          <t>4/5/2026 09:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Transport Cart 2</t>
+          <t>Transport Cart 1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>4/5/2026 12:49</t>
+          <t>4/5/2026 08:58</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>4/5/2026 09:01</t>
+          <t>4/5/2026 09:05</t>
         </is>
       </c>
     </row>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>30.86 min</t>
+          <t>29.90 min</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>84.67 min</t>
+          <t>82.33 min</t>
         </is>
       </c>
     </row>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>12.67 min</t>
+          <t>3.33 min</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>6.33/5.00/4.33 min</t>
+          <t>0.00/0.00/3.33 min</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1372,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>11.7010 sec</t>
+          <t>10.6310 sec</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1.9785 %</t>
+          <t>0.7225 %</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>30.71 min | 86.00 min</t>
+          <t>31.10 min | 86.00 min</t>
         </is>
       </c>
     </row>
@@ -1514,7 +1514,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>30.76 min | 83.00 min</t>
+          <t>28.86 min | 76.00 min</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>31.10 min | 85.00 min</t>
+          <t>29.76 min | 85.00 min</t>
         </is>
       </c>
     </row>
@@ -1553,7 +1553,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>23.64</v>
+        <v>11.82</v>
       </c>
     </row>
     <row r="34">
@@ -1563,7 +1563,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2.36</v>
+        <v>11.82</v>
       </c>
     </row>
     <row r="35">
@@ -1583,7 +1583,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>14.18</v>
+        <v>16.55</v>
       </c>
     </row>
     <row r="37">
@@ -1593,7 +1593,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4.61</v>
+        <v>3.69</v>
       </c>
     </row>
     <row r="38">
@@ -1603,7 +1603,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2.76</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="39">
@@ -1613,7 +1613,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>2.3</v>
+        <v>2.76</v>
       </c>
     </row>
     <row r="40">
@@ -1623,7 +1623,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>37.73</v>
+        <v>41.92</v>
       </c>
     </row>
     <row r="41">
@@ -1633,7 +1633,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>25.15</v>
+        <v>20.96</v>
       </c>
     </row>
     <row r="42">
@@ -1761,35 +1761,35 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>4/5/2026 10:48</t>
+          <t>4/5/2026 10:47</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>4/5/2026 10:50</t>
+          <t>4/5/2026 10:49</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>4/5/2026 10:50</t>
+          <t>4/5/2026 10:49</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>4/5/2026 11:20</t>
+          <t>4/5/2026 11:19</t>
         </is>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -2314,22 +2314,22 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>4/5/2026 08:41</t>
+          <t>4/5/2026 08:51</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>4/5/2026 08:45</t>
+          <t>4/5/2026 08:55</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M11" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12">
@@ -2554,22 +2554,22 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>4/5/2026 06:21</t>
+          <t>4/5/2026 06:20</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>4/5/2026 06:23</t>
+          <t>4/5/2026 06:22</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -2614,22 +2614,22 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>4/5/2026 10:47</t>
+          <t>4/5/2026 10:48</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>4/5/2026 10:56</t>
+          <t>4/5/2026 10:57</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -2721,35 +2721,35 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>4/5/2026 09:11</t>
+          <t>4/5/2026 09:10</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>4/5/2026 09:13</t>
+          <t>4/5/2026 09:12</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>4/5/2026 09:13</t>
+          <t>4/5/2026 09:12</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>4/5/2026 09:21</t>
+          <t>4/5/2026 09:20</t>
         </is>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3021,35 +3021,35 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>4/5/2026 08:01</t>
+          <t>4/5/2026 07:57</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>4/5/2026 08:02</t>
+          <t>4/5/2026 07:58</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>4/5/2026 08:10</t>
+          <t>4/5/2026 07:58</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>4/5/2026 08:37</t>
+          <t>4/5/2026 08:25</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="N23" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -3081,35 +3081,35 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>4/5/2026 12:06</t>
+          <t>4/5/2026 12:02</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>4/5/2026 12:08</t>
+          <t>4/5/2026 12:04</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>4/5/2026 12:11</t>
+          <t>4/5/2026 12:04</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>4/5/2026 12:57</t>
+          <t>4/5/2026 12:50</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="N24" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -3141,35 +3141,35 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
+          <t>4/5/2026 06:02</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
           <t>4/5/2026 06:03</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>4/5/2026 06:04</t>
-        </is>
-      </c>
       <c r="I25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>4/5/2026 06:04</t>
+          <t>4/5/2026 06:03</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>4/5/2026 06:06</t>
+          <t>4/5/2026 06:05</t>
         </is>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -3814,22 +3814,22 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>4/5/2026 06:21</t>
+          <t>4/5/2026 06:20</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>4/5/2026 06:23</t>
+          <t>4/5/2026 06:22</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -4028,25 +4028,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>4/5/2026 09:17</t>
+          <t>4/5/2026 09:16</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>4/5/2026 09:34</t>
+          <t>4/5/2026 09:33</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>4/5/2026 09:34</t>
+          <t>4/5/2026 09:33</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>4/5/2026 09:36</t>
+          <t>4/5/2026 09:35</t>
         </is>
       </c>
       <c r="I40" t="n">
@@ -4054,22 +4054,22 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>4/5/2026 09:36</t>
+          <t>4/5/2026 09:35</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>4/5/2026 09:56</t>
+          <t>4/5/2026 09:55</t>
         </is>
       </c>
       <c r="L40" t="n">
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -4088,48 +4088,48 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>4/5/2026 08:29</t>
+          <t>4/5/2026 08:20</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>4/5/2026 08:42</t>
+          <t>4/5/2026 08:33</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>4/5/2026 08:49</t>
+          <t>4/5/2026 08:33</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>4/5/2026 08:51</t>
+          <t>4/5/2026 08:35</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>4/5/2026 08:53</t>
+          <t>4/5/2026 08:35</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>4/5/2026 09:42</t>
+          <t>4/5/2026 09:24</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="N41" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -4294,22 +4294,22 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>4/5/2026 11:00</t>
+          <t>4/5/2026 10:59</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>4/5/2026 11:34</t>
+          <t>4/5/2026 11:33</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="N44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -4461,35 +4461,35 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>4/5/2026 10:00</t>
+          <t>4/5/2026 09:56</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>4/5/2026 10:02</t>
+          <t>4/5/2026 09:58</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>4/5/2026 10:02</t>
+          <t>4/5/2026 09:58</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>4/5/2026 10:09</t>
+          <t>4/5/2026 10:05</t>
         </is>
       </c>
       <c r="L47" t="n">
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="N47" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -4808,48 +4808,48 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>4/5/2026 07:35</t>
+          <t>4/5/2026 07:25</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>4/5/2026 07:39</t>
+          <t>4/5/2026 07:29</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
+          <t>4/5/2026 07:29</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>4/5/2026 07:31</t>
+        </is>
+      </c>
+      <c r="I53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>4/5/2026 07:31</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
           <t>4/5/2026 07:46</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>4/5/2026 07:48</t>
-        </is>
-      </c>
-      <c r="I53" t="n">
-        <v>7</v>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>4/5/2026 07:50</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>4/5/2026 08:05</t>
-        </is>
-      </c>
       <c r="L53" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="N53" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -5134,22 +5134,22 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>4/5/2026 07:26</t>
+          <t>4/5/2026 07:22</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>4/5/2026 07:33</t>
+          <t>4/5/2026 07:29</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="N58" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
